--- a/artfynd/A 54982-2021 artfynd.xlsx
+++ b/artfynd/A 54982-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54982-2021 artfynd.xlsx
+++ b/artfynd/A 54982-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99729428</v>
+        <v>68180655</v>
       </c>
       <c r="B2" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,56 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sköttbråten, Vrm</t>
+          <t>svensk anderstorp, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>371984.1976781108</v>
+        <v>371994</v>
       </c>
       <c r="R2" t="n">
-        <v>6681992.138162324</v>
+        <v>6682023</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +759,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1987-06-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1987-06-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,22 +773,441 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Jesper Berg Bylander</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Jesper Berg Bylander</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2485271</v>
+      </c>
+      <c r="B3" t="n">
+        <v>107719</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220015</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Hässleklocka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Campanula latifolia</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sköttbråten (12C7f14), Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>372085</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6682039</v>
+      </c>
+      <c r="S3" t="n">
+        <v>100</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Östmark</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2005-08-02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2005-08-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>120275141 / CAMP LAT / Tämligen allmän (2)  / OBJ.AREA:5,4 ha</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Björn Ehrenroth</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>99729428</v>
+      </c>
+      <c r="B4" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sköttbråten, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>371984</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6681992</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Östmark</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1987-06-14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1987-06-14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Rolf Tidemalm</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Rolf Tidemalm</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5021024</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sköttbråten (12C7f14), Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>372085</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6682039</v>
+      </c>
+      <c r="S5" t="n">
+        <v>100</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Östmark</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2005-08-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2005-08-02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>120275141 / HEPA NOB / Tämligen allmän (2)  / OBJ.AREA:5,4 ha</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Björn Ehrenroth</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5269544</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sköttbråten (12C7f14), Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>372085</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6682039</v>
+      </c>
+      <c r="S6" t="n">
+        <v>100</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Östmark</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2005-08-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2005-08-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>120275141 / ACTA SPI / Enstaka-sparsam (1)  / OBJ.AREA:5,4 ha</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Björn Ehrenroth</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54982-2021 artfynd.xlsx
+++ b/artfynd/A 54982-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68180655</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2485271</t>
         </is>
       </c>
     </row>
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99729428</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5021024</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1208,8 +1233,20 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5269544</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>